--- a/イベント一覧.xlsx
+++ b/イベント一覧.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sayur\OneDrive\デスクトップ\めも\my_app\260510 manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA86E63-4C67-4F9B-8ED0-1014821EC323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFAF3CDD-C2C3-4746-8427-F67FD5130483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" xr2:uid="{3435D29D-17A9-4A87-B931-BE3421F071AC}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" firstSheet="4" activeTab="9" xr2:uid="{3435D29D-17A9-4A87-B931-BE3421F071AC}"/>
   </bookViews>
   <sheets>
     <sheet name="氷原支配者" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="士官計画(日月)" sheetId="6" r:id="rId7"/>
     <sheet name="童心の宴" sheetId="2" r:id="rId8"/>
     <sheet name="野獣駆逐" sheetId="9" r:id="rId9"/>
-    <sheet name="サッカー" sheetId="11" r:id="rId10"/>
+    <sheet name="明月の盛典" sheetId="11" r:id="rId10"/>
     <sheet name="凛風の双王" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
